--- a/artfynd/A 54779-2024 artfynd.xlsx
+++ b/artfynd/A 54779-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>363081</v>
+        <v>344674</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601710.3358786192</v>
+        <v>601722</v>
       </c>
       <c r="R2" t="n">
-        <v>7160623.441416926</v>
+        <v>7160956</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2012-09-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-09-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>363078</v>
+        <v>344675</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601669.2831688746</v>
+        <v>601648</v>
       </c>
       <c r="R3" t="n">
-        <v>7160845.868417442</v>
+        <v>7160945</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,9 @@
           <t>2012-09-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-09-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>363080</v>
+        <v>363078</v>
       </c>
       <c r="B4" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601748.4267573024</v>
+        <v>601669</v>
       </c>
       <c r="R4" t="n">
-        <v>7160669.907929352</v>
+        <v>7160846</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +947,9 @@
           <t>2012-09-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-09-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>344675</v>
+        <v>363079</v>
       </c>
       <c r="B5" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601648.3149114762</v>
+        <v>601780</v>
       </c>
       <c r="R5" t="n">
-        <v>7160944.580829977</v>
+        <v>7160692</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1049,9 @@
           <t>2012-09-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2012-09-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>344674</v>
+        <v>363080</v>
       </c>
       <c r="B6" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601722.0575347615</v>
+        <v>601748</v>
       </c>
       <c r="R6" t="n">
-        <v>7160955.654958025</v>
+        <v>7160670</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,19 +1151,9 @@
           <t>2012-09-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2012-09-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>363079</v>
+        <v>363081</v>
       </c>
       <c r="B7" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601780.4210893657</v>
+        <v>601710</v>
       </c>
       <c r="R7" t="n">
-        <v>7160692.498684581</v>
+        <v>7160623</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,19 +1253,9 @@
           <t>2012-09-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2012-09-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
